--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_digit_manipulation.xlsx
@@ -750,14 +750,13 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -774,7 +773,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -784,17 +783,27 @@
 </t>
         </is>
       </c>
-      <c r="L4" s="3" t="n"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="N4" s="3" t="n"/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">8450
 </t>
         </is>
       </c>
@@ -804,10 +813,9 @@
 </t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2278
-</t>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>1178</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -816,9 +824,10 @@
 </t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
-        <is>
-          <t>6513</t>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -829,11 +838,11 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
@@ -847,13 +856,13 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -879,7 +888,7 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -897,7 +906,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -921,43 +930,43 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">8235
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">484
 </t>
         </is>
       </c>
@@ -967,19 +976,19 @@
 </t>
         </is>
       </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
+      <c r="S5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
+          <t xml:space="preserve">53
+</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -993,7 +1002,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -1005,13 +1014,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1043,7 +1052,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -1055,13 +1064,13 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1077,10 +1086,16 @@
 </t>
         </is>
       </c>
-      <c r="L6" s="3" t="n"/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1097,13 +1112,13 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>471</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1126,11 +1141,11 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
 </t>
@@ -1142,13 +1157,18 @@
 </t>
         </is>
       </c>
-      <c r="X6" s="8" t="inlineStr">
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">192
 </t>
         </is>
       </c>
-      <c r="Y6" s="3" t="n"/>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">578
+</t>
+        </is>
+      </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">140
@@ -1183,7 +1203,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -1195,59 +1215,55 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">149
 </t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">874
-</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1092
+          <t xml:space="preserve">54621561
+81
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">098
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="8" t="inlineStr">
+          <t xml:space="preserve">283412
+</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">304
 </t>
@@ -1261,13 +1277,13 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -1279,11 +1295,10 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="W7" s="8" t="inlineStr">
+          <t>70</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -1326,21 +1341,21 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -1350,16 +1365,21 @@
 </t>
         </is>
       </c>
-      <c r="I8" s="3" t="n"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1370,7 +1390,7 @@
 </t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">174
 </t>
@@ -1378,13 +1398,13 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1402,21 +1422,31 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="n"/>
-      <c r="U8" s="3" t="n"/>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">450
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1434,7 +1464,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11944
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -1457,16 +1487,20 @@
           <t>1458</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">887
+</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>630</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1477,41 +1511,45 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1346
-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2564
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">83
+</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">1717
+20 4
+89 8 6
+</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t xml:space="preserve">847
+</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1528,50 +1566,50 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2881
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>29381</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>134</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>957</t>
+          <t xml:space="preserve">957
+</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1591,87 +1629,86 @@
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">292
 </t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">847
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">212
@@ -1680,13 +1717,13 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -1698,31 +1735,31 @@
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1742,48 +1779,55 @@
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n"/>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="I11" s="3" t="n"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">861
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -1795,45 +1839,45 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t xml:space="preserve">890
+</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>484</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>9006</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
+          <t>7006</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>484</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">475
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -1845,19 +1889,18 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
-</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1888,7 +1931,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -1900,7 +1943,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1912,47 +1955,47 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">282
 </t>
@@ -1972,7 +2015,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">571
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -1990,7 +2033,7 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -2002,7 +2045,8 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t xml:space="preserve">60
+</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
@@ -2027,19 +2071,19 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">460
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -2051,13 +2095,13 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2069,10 +2113,16 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -2081,64 +2131,64 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">14
 </t>
         </is>
       </c>
-      <c r="Q13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0660
-</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
@@ -2147,7 +2197,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2173,7 +2223,7 @@
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -2183,7 +2233,12 @@
 </t>
         </is>
       </c>
-      <c r="F14" s="3" t="n"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">82
@@ -2198,103 +2253,102 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2134
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">462
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">521
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">745
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="S14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1182
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">393
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2320,139 +2374,137 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42292792
+64
+</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">646
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>2205</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">288
 </t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="R15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">080
-</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -2472,25 +2524,30 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n"/>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1939
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2498
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2501,41 +2558,43 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">994
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>725</t>
+          <t xml:space="preserve">34
+</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -2546,29 +2605,29 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
+          <t xml:space="preserve">1321
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">532
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2580,18 +2639,18 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t xml:space="preserve">933
+</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
@@ -2623,12 +2682,13 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2640,7 +2700,8 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">113
+61
 </t>
         </is>
       </c>
@@ -2652,8 +2713,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>007</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -2668,26 +2728,30 @@
 </t>
         </is>
       </c>
-      <c r="N17" s="3" t="n"/>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">2846
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">204
 </t>
@@ -2701,13 +2765,12 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
-</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2719,25 +2782,24 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2757,28 +2819,28 @@
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -2789,91 +2851,94 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>436</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>004</t>
+          <t xml:space="preserve">060
+</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>5041</t>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>0415</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t xml:space="preserve">468
+</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>691</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>8641</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">469
+</t>
+        </is>
+      </c>
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">062
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2890,99 +2955,100 @@
         </is>
       </c>
       <c r="C19" s="3" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n"/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
-      <c r="R19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2098
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -2994,7 +3060,7 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -3006,19 +3072,19 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">540
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3038,7 +3104,7 @@
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3050,37 +3116,37 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -3092,19 +3158,19 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="N20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8810
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -3128,48 +3194,49 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1485
+          <t xml:space="preserve">560
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="V20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">4654
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>505</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -3189,132 +3256,131 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>4170</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">266
 </t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">683
+</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">004
-</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="V21" s="3" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -3352,126 +3418,124 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">724
+</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">170
 </t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1880
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
+          <t xml:space="preserve">2678
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
+          <t xml:space="preserve">390
+</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">7268
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
@@ -3503,120 +3567,116 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5682
+          <t xml:space="preserve">562
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>348</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2850
+          <t xml:space="preserve">1850
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1039
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>711</t>
+          <t xml:space="preserve">1114
+</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">967
+          <t xml:space="preserve">683
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">956
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12385
+</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="n"/>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>31521</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -3636,7 +3696,7 @@
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -3646,27 +3706,27 @@
 </t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -3678,7 +3738,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -3690,18 +3750,19 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3713,24 +3774,25 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>804</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3742,31 +3804,31 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -3784,7 +3846,12 @@
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456
+</t>
+        </is>
+      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -3792,8 +3859,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -3803,13 +3869,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>166</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3826,7 +3891,7 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>471</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -3837,68 +3902,66 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>3564</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>6054</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>4381</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">835
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>6054</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -3924,84 +3987,88 @@
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">688
+</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
+</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">681
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">288
 </t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>3041</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">212
@@ -4010,7 +4077,8 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
@@ -4025,15 +4093,15 @@
 </t>
         </is>
       </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44944
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -4045,13 +4113,13 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4071,77 +4139,87 @@
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">026
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">214
 </t>
         </is>
       </c>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>4654</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1946
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
-      <c r="M27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -4160,7 +4238,7 @@
 </t>
         </is>
       </c>
-      <c r="U27" s="3" t="inlineStr">
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">158
 </t>
@@ -4180,7 +4258,7 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -4212,19 +4290,19 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -4234,21 +4312,21 @@
 </t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -4258,25 +4336,30 @@
 </t>
         </is>
       </c>
-      <c r="L28" s="8" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="n"/>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">34
@@ -4285,7 +4368,7 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -4297,49 +4380,49 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">956
+          <t xml:space="preserve">561
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -4365,13 +4448,13 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -4389,7 +4472,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -4401,11 +4484,11 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">184
 </t>
@@ -4413,12 +4496,12 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -4454,7 +4537,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -4464,9 +4547,9 @@
 </t>
         </is>
       </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2296
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">436
 </t>
         </is>
       </c>
@@ -4478,13 +4561,13 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4510,25 +4593,25 @@
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1334
+          <t xml:space="preserve">13532
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>858</t>
+          <t xml:space="preserve">858
+</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">474
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -4538,7 +4621,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4549,7 +4632,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4561,28 +4644,29 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>417</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">890
+</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1390
+          <t xml:space="preserve">1391
 </t>
         </is>
       </c>
@@ -4594,40 +4678,44 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="V30" s="3" t="n"/>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182
+</t>
+        </is>
+      </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>964</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>346</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>49811</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4646,7 +4734,7 @@
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4656,9 +4744,9 @@
 </t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">096
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4668,15 +4756,14 @@
 </t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>8761</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
@@ -4686,10 +4773,15 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4700,55 +4792,50 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">856
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="n"/>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">436
 </t>
         </is>
       </c>
@@ -4760,19 +4847,19 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4792,7 +4879,7 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -4816,74 +4903,75 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">726
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">12
 </t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>4824</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">868
-</t>
-        </is>
-      </c>
-      <c r="P32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">924
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -4895,7 +4983,7 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4913,7 +5001,7 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4945,13 +5033,13 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4963,25 +5051,25 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4999,23 +5087,23 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">866
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="8" t="inlineStr">
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">266
 </t>
@@ -5029,44 +5117,49 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">560
-</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">218
 </t>
         </is>
       </c>
-      <c r="V33" s="3" t="n"/>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">750
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -5084,7 +5177,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">282
 </t>
@@ -5098,13 +5191,13 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5116,7 +5209,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -5128,7 +5221,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -5138,7 +5231,7 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="8" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">172
 </t>
@@ -5146,13 +5239,13 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -5162,7 +5255,7 @@
 </t>
         </is>
       </c>
-      <c r="Q34" s="8" t="inlineStr">
+      <c r="Q34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">282
 </t>
@@ -5176,13 +5269,13 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">576
 </t>
         </is>
       </c>
@@ -5200,7 +5293,7 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5212,13 +5305,13 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -5238,7 +5331,7 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5250,7 +5343,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -5260,67 +5353,72 @@
 </t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0
+</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9006
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">170
 </t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="n"/>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
@@ -5329,43 +5427,43 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
-</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
@@ -5383,121 +5481,125 @@
         </is>
       </c>
       <c r="C36" s="3" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">486
+</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">756
+</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">726
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">835
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N36" s="8" t="inlineStr">
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">618
+</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">564
+</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="T36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">564
-</t>
-        </is>
-      </c>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="V36" s="3" t="n"/>
-      <c r="W36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -5506,13 +5608,13 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">352
 </t>
         </is>
       </c>
@@ -5532,7 +5634,7 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">1328
 </t>
         </is>
       </c>
@@ -5544,14 +5646,13 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">456
-</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -5562,13 +5663,13 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
@@ -5579,77 +5680,81 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
-</t>
+          <t>8461</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t xml:space="preserve">999
+</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11395
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1318
+          <t xml:space="preserve">1348
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">19228
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1017
-</t>
-        </is>
-      </c>
-      <c r="T37" s="3" t="n"/>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">564
+</t>
+        </is>
+      </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3868
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
@@ -5675,59 +5780,60 @@
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">921
 </t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8950
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">7
+9
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>273</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -5739,7 +5845,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
+          <t xml:space="preserve">7378
 </t>
         </is>
       </c>
@@ -5751,55 +5857,56 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">77
+248
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">117
+203
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>00578</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="W38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -5829,27 +5936,27 @@
 </t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5867,8 +5974,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -5879,84 +5985,85 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">861
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22084
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">394
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5988,26 +6095,25 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -6018,22 +6124,22 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>1941</t>
-        </is>
-      </c>
-      <c r="M40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="N40" s="8" t="inlineStr">
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
@@ -6041,25 +6147,25 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
-        </is>
-      </c>
-      <c r="P40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="R40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
@@ -6071,43 +6177,43 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">354
+</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">919
-</t>
-        </is>
-      </c>
-      <c r="W40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -6127,32 +6233,37 @@
       <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
+          <t xml:space="preserve">429
+</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="F41" s="3" t="n"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6164,7 +6275,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -6174,82 +6285,82 @@
 </t>
         </is>
       </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
+      <c r="M41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">721
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">8401
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="n"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">765
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">765
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6267,7 +6378,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
@@ -6275,49 +6386,49 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">708
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -6329,25 +6440,25 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
@@ -6365,36 +6476,46 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
+          <t xml:space="preserve">625
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">264
 </t>
         </is>
       </c>
-      <c r="V42" s="3" t="n"/>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="n"/>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -6417,16 +6538,16 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">154
 </t>
@@ -6439,11 +6560,11 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="J43" s="8" t="inlineStr">
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
@@ -6451,13 +6572,13 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -6469,7 +6590,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6481,31 +6602,31 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
@@ -6517,7 +6638,7 @@
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -6527,19 +6648,24 @@
 </t>
         </is>
       </c>
-      <c r="X43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4270
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">570
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -6556,114 +6682,127 @@
       <c r="C44" s="3" t="n"/>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n"/>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n"/>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">773
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">76
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>7661</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">626
+</t>
+        </is>
+      </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">470
+</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="N44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
-      <c r="P44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">650
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t>7650</t>
-        </is>
-      </c>
-      <c r="R44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1470
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="n"/>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
@@ -6687,42 +6826,42 @@
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
@@ -6734,92 +6873,89 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t xml:space="preserve">1396
+</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">9984
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>0526</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">1141
+41 1
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t xml:space="preserve">275
+</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01111
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1071
+          <t xml:space="preserve">3179
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1439
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">655
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">644
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6836,25 +6972,26 @@
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">89
+6
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6876,10 +7013,15 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -6891,53 +7033,55 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">1141
+41 1
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9179
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
+          <t xml:space="preserve">2919292795
+24
+12
+</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
@@ -6945,25 +7089,25 @@
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">655
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_digit_manipulation.xlsx
@@ -735,24 +735,54 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 4
+</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 </t>
         </is>
       </c>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n"/>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -760,18 +790,33 @@
         </is>
       </c>
       <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">840
 </t>
         </is>
       </c>
-      <c r="P4" s="3" t="n"/>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1 39
+</t>
+        </is>
+      </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -781,9 +826,24 @@
 </t>
         </is>
       </c>
-      <c r="S4" s="3" t="n"/>
-      <c r="T4" s="3" t="n"/>
-      <c r="U4" s="3" t="n"/>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">548
+</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="V4" s="3" t="n"/>
       <c r="W4" s="3" t="n"/>
       <c r="X4" s="3" t="n"/>
@@ -803,45 +863,105 @@
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
+          <t xml:space="preserve">004
+</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1289
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">830
+</t>
+        </is>
+      </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="n"/>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
         </is>
       </c>
-      <c r="S5" s="3" t="n"/>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
@@ -857,7 +977,7 @@
 </t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="W5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
@@ -895,17 +1015,26 @@
         </is>
       </c>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0108
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -915,44 +1044,79 @@
 </t>
         </is>
       </c>
-      <c r="I6" s="3" t="n"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="3" t="n"/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
+          <t xml:space="preserve">6564
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -960,7 +1124,7 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -1004,22 +1168,43 @@
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -1029,21 +1214,50 @@
 </t>
         </is>
       </c>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>4841</t>
+        </is>
+      </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="n"/>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
       <c r="P7" s="3" t="n"/>
-      <c r="Q7" s="3" t="n"/>
-      <c r="R7" s="3" t="n"/>
-      <c r="S7" s="3" t="n"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1464
+          <t xml:space="preserve">1426
 </t>
         </is>
       </c>
@@ -1053,7 +1267,12 @@
 </t>
         </is>
       </c>
-      <c r="V7" s="3" t="n"/>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">196
@@ -1062,18 +1281,19 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">19
+</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -1093,40 +1313,65 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" s="3" t="n"/>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="n"/>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
       <c r="P8" s="3" t="n"/>
       <c r="Q8" s="3" t="inlineStr">
         <is>
@@ -1134,7 +1379,12 @@
 </t>
         </is>
       </c>
-      <c r="R8" s="3" t="n"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">197
@@ -1143,26 +1393,31 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">450
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="n"/>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -1189,30 +1444,44 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1458</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
+          <t xml:space="preserve">1428
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">887
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1152
+</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">571
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t xml:space="preserve">824
+</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">346
+</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t xml:space="preserve">266
+</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1223,18 +1492,25 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">917
+</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="n"/>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
+</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">423
 </t>
         </is>
       </c>
@@ -1246,59 +1522,61 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19438
+          <t xml:space="preserve">1428
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10960
+          <t xml:space="preserve">1060
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1008
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011
+          <t xml:space="preserve">20991
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">9926
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">2299
+</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">6150
 </t>
         </is>
       </c>
@@ -1318,119 +1596,138 @@
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t xml:space="preserve">292
+</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
+          <t>04</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">69
+</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t xml:space="preserve">113
+</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="n"/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">847
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="Q10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9438
-</t>
-        </is>
-      </c>
-      <c r="R10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0960
-</t>
-        </is>
-      </c>
-      <c r="S10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1026
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>1631</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>294610</t>
+          <t xml:space="preserve">510
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>9114</t>
-        </is>
-      </c>
-      <c r="X10" s="3" t="n"/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">889
+</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -1448,98 +1745,114 @@
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n"/>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="M11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="n"/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="n"/>
+          <t xml:space="preserve">8909
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="Q11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="n"/>
-      <c r="T11" s="3" t="n"/>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="n"/>
       <c r="V11" s="3" t="n"/>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
+      <c r="W11" s="3" t="n"/>
       <c r="X11" s="3" t="n"/>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
+      <c r="Y11" s="3" t="n"/>
+      <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1553,48 +1866,75 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">513
+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="8" t="inlineStr">
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">116
 </t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1820
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -1604,64 +1944,64 @@
 </t>
         </is>
       </c>
-      <c r="P12" s="3" t="n"/>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="R12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="S12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29412
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">096
-</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="n"/>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">971
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">600
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1678,100 +2018,144 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 1
+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n"/>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n"/>
+          <t xml:space="preserve">2835
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="R13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="S13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29412
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="n"/>
+          <t xml:space="preserve">511
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="V13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">096
-</t>
-        </is>
-      </c>
-      <c r="W13" s="8" t="inlineStr">
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="X13" s="3" t="n"/>
-      <c r="Y13" s="3" t="n"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600
+</t>
+        </is>
+      </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1789,70 +2173,105 @@
         </is>
       </c>
       <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n"/>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">331
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1916
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="n"/>
-      <c r="R14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">745
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">868
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="S14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -1864,26 +2283,30 @@
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="n"/>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>034</t>
+        </is>
+      </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -1901,86 +2324,135 @@
         </is>
       </c>
       <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="n"/>
-      <c r="Q15" s="3" t="n"/>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="n"/>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="n"/>
-      <c r="X15" s="3" t="n"/>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
@@ -2000,69 +2472,138 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
-</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
+          <t xml:space="preserve">11988
+</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0909
+</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11139
+</t>
+        </is>
+      </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11910
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9006
+</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9808
+</t>
+        </is>
+      </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="n"/>
-      <c r="P16" s="3" t="n"/>
-      <c r="Q16" s="3" t="n"/>
-      <c r="R16" s="3" t="n"/>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9200
+</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182
+</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22812
+</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1041
+</t>
+        </is>
+      </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="T16" s="3" t="n"/>
-      <c r="U16" s="3" t="n"/>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2662
+</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="n"/>
+          <t xml:space="preserve">1528
+</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">945
+</t>
+        </is>
+      </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">3048
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -2079,124 +2620,142 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1288
-</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">098
-</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>1344</t>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">498
+          <t xml:space="preserve">001
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>920</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">840
 </t>
         </is>
       </c>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1282
-</t>
-        </is>
-      </c>
-      <c r="R17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">029
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2662
-</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="n"/>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">522
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>1481</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">993
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020
+          <t xml:space="preserve">684
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -2213,90 +2772,140 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">278
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 1
+</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">804
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">621
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="n"/>
-      <c r="N18" s="3" t="n"/>
-      <c r="O18" s="3" t="n"/>
-      <c r="P18" s="3" t="n"/>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="n"/>
-      <c r="S18" s="3" t="n"/>
-      <c r="T18" s="3" t="n"/>
-      <c r="U18" s="3" t="n"/>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">488
+</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X18" s="3" t="n"/>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1604
-</t>
-        </is>
-      </c>
-      <c r="Z18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="n"/>
+      <c r="Z18" s="3" t="n"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -2313,74 +2922,133 @@
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
+          <t xml:space="preserve">17 6
+</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="n"/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">468
 </t>
         </is>
       </c>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
-      <c r="P19" s="3" t="n"/>
-      <c r="Q19" s="3" t="n"/>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="n"/>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29481
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="n"/>
-      <c r="V19" s="3" t="n"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="Y19" s="3" t="n"/>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">340
+</t>
+        </is>
+      </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11495
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -2398,56 +3066,136 @@
         </is>
       </c>
       <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
       <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
-</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="n"/>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3" t="n"/>
-      <c r="O20" s="3" t="n"/>
-      <c r="P20" s="3" t="n"/>
-      <c r="Q20" s="3" t="n"/>
-      <c r="R20" s="3" t="n"/>
-      <c r="S20" s="3" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1174
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
-</t>
-        </is>
-      </c>
-      <c r="U20" s="3" t="n"/>
-      <c r="V20" s="3" t="n"/>
-      <c r="W20" s="3" t="n"/>
+          <t xml:space="preserve">488
+</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
 </t>
         </is>
       </c>
-      <c r="Y20" s="3" t="n"/>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">580
+</t>
+        </is>
+      </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -2465,51 +3213,136 @@
         </is>
       </c>
       <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">004
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="n"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">590
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2880
-</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n"/>
-      <c r="Q21" s="3" t="n"/>
-      <c r="R21" s="3" t="n"/>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9485
-</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="n"/>
-      <c r="V21" s="3" t="n"/>
-      <c r="W21" s="3" t="n"/>
-      <c r="X21" s="3" t="n"/>
-      <c r="Y21" s="3" t="n"/>
-      <c r="Z21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
@@ -2527,60 +3360,136 @@
         </is>
       </c>
       <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n"/>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n"/>
-      <c r="Q22" s="3" t="n"/>
-      <c r="R22" s="3" t="n"/>
-      <c r="S22" s="3" t="n"/>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060
-</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="n"/>
+          <t xml:space="preserve">683
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="W22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="n"/>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -2597,26 +3506,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1956
+</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">894
+</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n"/>
+          <t xml:space="preserve">848
+</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
+</t>
+        </is>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">529
 </t>
         </is>
       </c>
@@ -2626,53 +3560,92 @@
 </t>
         </is>
       </c>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">924
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">880
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="n"/>
-      <c r="Q23" s="3" t="n"/>
+          <t xml:space="preserve">9268
+</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1404
+</t>
+        </is>
+      </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="n"/>
+          <t xml:space="preserve">1034
+</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11804
+</t>
+        </is>
+      </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683
-</t>
-        </is>
-      </c>
-      <c r="U23" s="3" t="n"/>
+          <t xml:space="preserve">2679
+</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">919
+</t>
+        </is>
+      </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="n"/>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418
+</t>
+        </is>
+      </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">22161
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -2689,128 +3662,142 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9456
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>841</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>311</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n"/>
-      <c r="O24" s="3" t="n"/>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">854
+</t>
+        </is>
+      </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="R24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1034
-</t>
-        </is>
-      </c>
-      <c r="S24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0804
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12678
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1235
-</t>
-        </is>
-      </c>
-      <c r="W24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -2827,99 +3814,129 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 1 5
+</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="n"/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="n"/>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">028
+</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">569
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">829
+</t>
+        </is>
+      </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2218
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="n"/>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="n"/>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="n"/>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">864
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="n"/>
       <c r="Y25" s="3" t="n"/>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
+      <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2933,70 +3950,149 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n"/>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="3" t="n"/>
-      <c r="P26" s="3" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">698
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="n"/>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="n"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="n"/>
-      <c r="Y26" s="3" t="n"/>
-      <c r="Z26" s="3" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">385
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -3010,51 +4106,97 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 0
+</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="n"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="3" t="inlineStr">
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="N27" s="3" t="n"/>
-      <c r="O27" s="3" t="n"/>
-      <c r="P27" s="3" t="n"/>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="n"/>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1889
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="n"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">207
@@ -3063,19 +4205,34 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="n"/>
-      <c r="W27" s="3" t="n"/>
-      <c r="X27" s="3" t="n"/>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
       <c r="Y27" s="3" t="n"/>
       <c r="Z27" s="3" t="n"/>
       <c r="AA27" s="3" t="inlineStr">
@@ -3092,52 +4249,127 @@
         </is>
       </c>
       <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="F28" s="3" t="n"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="n"/>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="n"/>
-      <c r="L28" s="3" t="n"/>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="n"/>
-      <c r="O28" s="3" t="n"/>
-      <c r="P28" s="3" t="n"/>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52940
+</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="n"/>
-      <c r="S28" s="3" t="n"/>
-      <c r="T28" s="3" t="n"/>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">567
+</t>
+        </is>
+      </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="n"/>
-      <c r="W28" s="3" t="n"/>
-      <c r="X28" s="3" t="n"/>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="Y28" s="3" t="n"/>
       <c r="Z28" s="3" t="n"/>
       <c r="AA28" s="3" t="inlineStr">
@@ -3154,49 +4386,144 @@
         </is>
       </c>
       <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="n"/>
-      <c r="P29" s="3" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="n"/>
-      <c r="S29" s="3" t="n"/>
-      <c r="T29" s="3" t="n"/>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6595
+</t>
+        </is>
+      </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="X29" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">128
 </t>
         </is>
       </c>
-      <c r="V29" s="3" t="n"/>
-      <c r="W29" s="3" t="n"/>
-      <c r="X29" s="3" t="n"/>
-      <c r="Y29" s="3" t="n"/>
-      <c r="Z29" s="3" t="n"/>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">662
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -3211,86 +4538,141 @@
         </is>
       </c>
       <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19524
+</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">808
+</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18168
+</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">474
+</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1310
+</t>
+        </is>
+      </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="n"/>
+          <t xml:space="preserve">20161
+</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26814
+</t>
+        </is>
+      </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">914
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">8365
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="n"/>
+          <t xml:space="preserve">4200
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">1320
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">10820
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T30" s="3" t="n"/>
+          <t xml:space="preserve">1022
+</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2989
+</t>
+        </is>
+      </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="V30" s="3" t="n"/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18182
+</t>
+        </is>
+      </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X30" s="3" t="n"/>
-      <c r="Y30" s="3" t="n"/>
+          <t xml:space="preserve">9856
+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">919
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3162
+</t>
+        </is>
+      </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">498
 </t>
         </is>
       </c>
@@ -3307,98 +4689,142 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3098
-</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">474
-</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8100
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">314
-</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">914
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3183
 </t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3" t="n"/>
-      <c r="P31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="Q31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">320
-</t>
-        </is>
-      </c>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">020
-</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="n"/>
-      <c r="T31" s="3" t="n"/>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">856
+</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">598
+</t>
+        </is>
+      </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>304</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="n"/>
-      <c r="Y31" s="3" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">692
+</t>
+        </is>
+      </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2498
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3415,90 +4841,145 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n"/>
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="8" t="inlineStr">
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">868
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">568
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">808
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="n"/>
-      <c r="P32" s="3" t="n"/>
-      <c r="Q32" s="3" t="n"/>
-      <c r="R32" s="3" t="n"/>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="n"/>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">948
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="n"/>
-      <c r="X32" s="3" t="n"/>
-      <c r="Y32" s="3" t="n"/>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3512,109 +4993,141 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">94
+</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t xml:space="preserve">286
+</t>
         </is>
       </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">560
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">750
 </t>
         </is>
       </c>
@@ -3633,57 +5146,132 @@
         </is>
       </c>
       <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="n"/>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="n"/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n"/>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="n"/>
-      <c r="S34" s="3" t="n"/>
-      <c r="T34" s="3" t="n"/>
-      <c r="U34" s="3" t="n"/>
-      <c r="V34" s="3" t="n"/>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="R34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0216
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">572
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2846
+</t>
+        </is>
+      </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="n"/>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="n"/>
       <c r="Z34" s="3" t="n"/>
       <c r="AA34" s="3" t="inlineStr">
@@ -3699,60 +5287,135 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">839
+</t>
+        </is>
+      </c>
+      <c r="P35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="R35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1908
+</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n"/>
-      <c r="Q35" s="3" t="n"/>
-      <c r="R35" s="3" t="n"/>
-      <c r="S35" s="3" t="n"/>
-      <c r="T35" s="3" t="n"/>
-      <c r="U35" s="3" t="n"/>
-      <c r="V35" s="3" t="n"/>
-      <c r="W35" s="3" t="n"/>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">622
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="W35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -3771,44 +5434,143 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
-      <c r="J36" s="3" t="n"/>
-      <c r="K36" s="3" t="n"/>
-      <c r="L36" s="3" t="n"/>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="n"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">486
+</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="n"/>
-      <c r="Q36" s="3" t="n"/>
-      <c r="R36" s="3" t="n"/>
-      <c r="S36" s="3" t="n"/>
-      <c r="T36" s="3" t="n"/>
+          <t xml:space="preserve">870
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="V36" s="3" t="n"/>
-      <c r="W36" s="3" t="n"/>
+          <t>4608</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="Y36" s="3" t="n"/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
       <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3824,59 +5586,144 @@
         </is>
       </c>
       <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="3" t="n"/>
-      <c r="J37" s="3" t="n"/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11208
+</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">802
+</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1110
+</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">996
+</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8080
+</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218164
+</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2198
+</t>
+        </is>
+      </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
+          <t xml:space="preserve">905
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0116
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10822
+</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="n"/>
-      <c r="Q37" s="3" t="n"/>
-      <c r="R37" s="3" t="n"/>
-      <c r="S37" s="3" t="n"/>
+          <t xml:space="preserve">49208
+</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1328
+</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11022
+</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1019
+</t>
+        </is>
+      </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">2886
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="n"/>
-      <c r="W37" s="3" t="n"/>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1098
+</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="Y37" s="3" t="n"/>
-      <c r="Z37" s="3" t="n"/>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1068
+</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2312
+</t>
+        </is>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3891,100 +5738,139 @@
         </is>
       </c>
       <c r="C38" s="3" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1308
-</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">486
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>415</t>
+          <t xml:space="preserve">42
+</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
-        </is>
-      </c>
-      <c r="K38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">951
 </t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>8661</t>
-        </is>
-      </c>
-      <c r="N38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">924208
-</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="n"/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">861
+</t>
+        </is>
+      </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Q38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">398
-</t>
-        </is>
-      </c>
-      <c r="R38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">022
-</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="n"/>
-      <c r="T38" s="3" t="n"/>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1481
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">387
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="n"/>
-      <c r="X38" s="3" t="n"/>
-      <c r="Y38" s="3" t="n"/>
-      <c r="Z38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39312
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">772
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3998,94 +5884,141 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="n"/>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">026
+</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="I39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">421
+          <t>468</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n"/>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="n"/>
-      <c r="O39" s="3" t="n"/>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8986
+</t>
+        </is>
+      </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">418
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="n"/>
+          <t xml:space="preserve">408
+</t>
+        </is>
+      </c>
+      <c r="S39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">577
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="n"/>
-      <c r="Y39" s="3" t="n"/>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="X39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">698
+</t>
+        </is>
+      </c>
       <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -4100,66 +6033,141 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="3" t="n"/>
-      <c r="N40" s="3" t="n"/>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">840
 </t>
         </is>
       </c>
-      <c r="P40" s="3" t="n"/>
-      <c r="Q40" s="3" t="n"/>
-      <c r="R40" s="3" t="n"/>
-      <c r="S40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="n"/>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="X40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
@@ -4177,59 +6185,138 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="3" t="n"/>
-      <c r="L41" s="3" t="n"/>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n"/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8401
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="n"/>
-      <c r="Q41" s="3" t="n"/>
-      <c r="R41" s="3" t="n"/>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="n"/>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="n"/>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="n"/>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">623
+</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1084
+</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="n"/>
+          <t xml:space="preserve">765
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -4243,30 +6330,91 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="n"/>
-      <c r="G42" s="3" t="n"/>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1916
-</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="n"/>
-      <c r="L42" s="3" t="n"/>
-      <c r="M42" s="3" t="n"/>
-      <c r="N42" s="3" t="n"/>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>85401</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="n"/>
-      <c r="Q42" s="3" t="n"/>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">210
@@ -4274,13 +6422,48 @@
         </is>
       </c>
       <c r="S42" s="3" t="n"/>
-      <c r="T42" s="3" t="n"/>
-      <c r="U42" s="3" t="n"/>
-      <c r="V42" s="3" t="n"/>
-      <c r="W42" s="3" t="n"/>
-      <c r="X42" s="3" t="n"/>
-      <c r="Y42" s="3" t="n"/>
-      <c r="Z42" s="3" t="n"/>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">520
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="X42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">570
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4295,54 +6478,143 @@
         </is>
       </c>
       <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="n"/>
-      <c r="F43" s="3" t="n"/>
-      <c r="G43" s="3" t="n"/>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1722
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="n"/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="K43" s="3" t="n"/>
-      <c r="L43" s="3" t="n"/>
-      <c r="M43" s="3" t="n"/>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="n"/>
-      <c r="P43" s="3" t="n"/>
-      <c r="Q43" s="3" t="n"/>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">094
+</t>
+        </is>
+      </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="n"/>
-      <c r="T43" s="3" t="n"/>
-      <c r="U43" s="3" t="n"/>
-      <c r="V43" s="3" t="n"/>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
+      <c r="S43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">426
+</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">570
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">148
 </t>
         </is>
       </c>
-      <c r="Z43" s="3" t="n"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4357,60 +6629,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n"/>
+          <t xml:space="preserve">800
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="I44" s="3" t="n"/>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="n"/>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
+      <c r="N44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
         </is>
       </c>
-      <c r="O44" s="3" t="n"/>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">808
+</t>
+        </is>
+      </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -4426,17 +6714,42 @@
 </t>
         </is>
       </c>
-      <c r="S44" s="3" t="n"/>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">470
 </t>
         </is>
       </c>
-      <c r="U44" s="3" t="n"/>
-      <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="W44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
@@ -4457,13 +6770,33 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0221
+</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2884
+</t>
+        </is>
+      </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">600
 </t>
         </is>
       </c>
@@ -4475,7 +6808,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -4487,13 +6820,13 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
+          <t xml:space="preserve">11896
 </t>
         </is>
       </c>
@@ -4503,8 +6836,18 @@
 </t>
         </is>
       </c>
-      <c r="N45" s="3" t="n"/>
-      <c r="O45" s="3" t="n"/>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11027
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179926
+</t>
+        </is>
+      </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -4513,15 +6856,25 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16560
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="n"/>
-      <c r="S45" s="3" t="n"/>
+          <t xml:space="preserve">16620
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1210
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">2179
 </t>
         </is>
       </c>
@@ -4531,12 +6884,27 @@
 </t>
         </is>
       </c>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="n"/>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1928
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3228
+</t>
+        </is>
+      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">644
 </t>
         </is>
       </c>
@@ -4555,16 +6923,21 @@
         </is>
       </c>
       <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">719
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -4576,13 +6949,13 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -4599,8 +6972,18 @@
 </t>
         </is>
       </c>
-      <c r="M46" s="3" t="n"/>
-      <c r="N46" s="3" t="n"/>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">854
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">831
@@ -4613,22 +6996,42 @@
 </t>
         </is>
       </c>
-      <c r="Q46" s="3" t="n"/>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">201
 </t>
         </is>
       </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n"/>
-      <c r="U46" s="8" t="inlineStr">
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="V46" s="3" t="n"/>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -4637,13 +7040,13 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_digit_manipulation.xlsx
@@ -735,12 +735,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 4
-</t>
-        </is>
-      </c>
+      <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">278
@@ -767,7 +762,7 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -789,10 +784,15 @@
 </t>
         </is>
       </c>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -810,13 +810,13 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 1 39
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -828,7 +828,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -911,15 +911,15 @@
 </t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1289
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -935,12 +935,7 @@
 </t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
+      <c r="P5" s="3" t="n"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">284
@@ -961,7 +956,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -977,7 +972,7 @@
 </t>
         </is>
       </c>
-      <c r="W5" s="8" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
@@ -991,7 +986,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -1017,7 +1012,7 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1064,7 +1059,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -1088,7 +1083,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -1112,7 +1107,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6564
+          <t xml:space="preserve">664
 </t>
         </is>
       </c>
@@ -1178,12 +1173,7 @@
 </t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
+      <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">126
@@ -1204,7 +1194,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -1216,13 +1206,14 @@
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t xml:space="preserve">074
+</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1237,7 +1228,12 @@
 </t>
         </is>
       </c>
-      <c r="P7" s="3" t="n"/>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">304
@@ -1252,12 +1248,13 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
@@ -1269,8 +1266,7 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
@@ -1281,19 +1277,19 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -1313,13 +1309,13 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -1329,15 +1325,15 @@
 </t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -1349,7 +1345,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1393,7 +1389,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">450
+          <t xml:space="preserve">459
 </t>
         </is>
       </c>
@@ -1403,7 +1399,7 @@
 </t>
         </is>
       </c>
-      <c r="V8" s="8" t="inlineStr">
+      <c r="V8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
 </t>
@@ -1454,15 +1450,10 @@
 </t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1152
-</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">571
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
@@ -1474,13 +1465,12 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
-</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">864
 </t>
         </is>
       </c>
@@ -1498,19 +1488,19 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">098
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">423
+          <t xml:space="preserve">4235
 </t>
         </is>
       </c>
@@ -1522,49 +1512,49 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">1860
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20991
+          <t xml:space="preserve">2631
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9926
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -1576,7 +1566,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6150
+          <t xml:space="preserve">680
 </t>
         </is>
       </c>
@@ -1594,7 +1584,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">292
 </t>
@@ -1602,24 +1592,25 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -1637,28 +1628,28 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">511
 </t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">847
@@ -1667,7 +1658,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1691,7 +1682,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -1721,7 +1712,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
@@ -1745,16 +1736,14 @@
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>465</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1765,8 +1754,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>416</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1777,8 +1765,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>546</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1799,9 +1786,9 @@
 </t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -1813,7 +1800,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8909
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -1823,9 +1810,9 @@
 </t>
         </is>
       </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -1843,7 +1830,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">475
 </t>
         </is>
       </c>
@@ -1866,15 +1853,10 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">513
-</t>
-        </is>
-      </c>
+      <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -1934,7 +1916,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1952,11 +1934,11 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="R12" s="8" t="inlineStr">
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">216
 </t>
@@ -1970,7 +1952,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -1987,9 +1969,9 @@
 </t>
         </is>
       </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">971
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -2001,7 +1983,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -2018,94 +2000,91 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 1
-</t>
-        </is>
-      </c>
+      <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2835
-</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">199
@@ -2114,22 +2093,23 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
+          <t xml:space="preserve">571
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
@@ -2149,16 +2129,10 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+          <t>7640</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="n"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -2185,22 +2159,16 @@
 </t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">331
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>478</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -2209,7 +2177,7 @@
 </t>
         </is>
       </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">110
 </t>
@@ -2233,9 +2201,9 @@
 </t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">878
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -2251,9 +2219,9 @@
 </t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">868
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2263,7 +2231,7 @@
 </t>
         </is>
       </c>
-      <c r="S14" s="8" t="inlineStr">
+      <c r="S14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
@@ -2277,7 +2245,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -2289,7 +2257,8 @@
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>034</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
@@ -2300,7 +2269,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -2336,9 +2305,9 @@
 </t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
@@ -2367,9 +2336,9 @@
         </is>
       </c>
       <c r="K15" s="3" t="n"/>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -2387,13 +2356,14 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">134
+</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -2472,16 +2442,11 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11988
-</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0909
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">10388
+</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">11139
@@ -2496,22 +2461,21 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>30191</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">906
 </t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9006
-</t>
-        </is>
-      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -2520,8 +2484,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9808
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -2532,36 +2495,31 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t xml:space="preserve">904
+</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9200
-</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1182
-</t>
-        </is>
-      </c>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22812
+          <t xml:space="preserve">8382
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
+          <t xml:space="preserve">1021
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -2579,31 +2537,30 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1528
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>933</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3048
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -2620,15 +2577,10 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -2652,7 +2604,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2675,7 +2627,7 @@
 </t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -2689,13 +2641,13 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2707,7 +2659,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -2725,7 +2677,7 @@
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -2737,19 +2689,18 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
+          <t xml:space="preserve">604
 </t>
         </is>
       </c>
@@ -2772,37 +2723,25 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 1
-</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">804
-</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>84</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">136
 </t>
@@ -2814,27 +2753,26 @@
 </t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>136</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">621
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -2846,31 +2784,31 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">788
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2888,8 +2826,7 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>464</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -2919,7 +2856,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">296
@@ -2938,7 +2880,7 @@
 </t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">118
 </t>
@@ -2946,7 +2888,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 6
+          <t xml:space="preserve">17 5
 </t>
         </is>
       </c>
@@ -2964,7 +2906,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
@@ -2974,7 +2916,7 @@
 </t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">172
 </t>
@@ -2988,14 +2930,13 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>701</t>
         </is>
       </c>
       <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -3013,18 +2954,19 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>940</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -3042,13 +2984,13 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3068,7 +3010,7 @@
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -3093,7 +3035,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
@@ -3105,7 +3047,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -3115,9 +3057,9 @@
 </t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1174
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -3165,8 +3107,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -3189,7 +3130,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
@@ -3215,7 +3156,7 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -3227,7 +3168,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3251,19 +3192,19 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3275,7 +3216,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -3306,13 +3247,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">2560
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -3328,15 +3269,14 @@
 </t>
         </is>
       </c>
-      <c r="X21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
@@ -3362,19 +3302,19 @@
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -3452,7 +3392,7 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3468,7 +3408,7 @@
 </t>
         </is>
       </c>
-      <c r="V22" s="3" t="inlineStr">
+      <c r="V22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
@@ -3480,10 +3420,14 @@
 </t>
         </is>
       </c>
-      <c r="X22" s="3" t="n"/>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>1551</t>
+        </is>
+      </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -3506,15 +3450,10 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1956
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -3526,31 +3465,30 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">5295
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -3562,7 +3500,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -3574,49 +3512,48 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9268
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
+          <t xml:space="preserve">1039
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11804
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2679
+          <t xml:space="preserve">82678
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>976</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -3627,25 +3564,24 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22161
-</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3662,12 +3598,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">291
@@ -3680,21 +3611,21 @@
 </t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">375
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -3710,7 +3641,12 @@
 </t>
         </is>
       </c>
-      <c r="K24" s="3" t="n"/>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51
+</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -3767,7 +3703,7 @@
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3785,7 +3721,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3814,26 +3750,22 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8 1 5
-</t>
-        </is>
-      </c>
+      <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -3845,13 +3777,13 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -3863,46 +3795,41 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">028
-</t>
-        </is>
-      </c>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2218
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="n"/>
       <c r="R25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -3911,8 +3838,7 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
@@ -3924,13 +3850,13 @@
       <c r="U25" s="3" t="n"/>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">864
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3952,7 +3878,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3962,39 +3888,39 @@
 </t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">022
+</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -4016,14 +3942,10 @@
 </t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
+      <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -4059,13 +3981,12 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
+          <t>438</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">494
 </t>
         </is>
       </c>
@@ -4083,14 +4004,13 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">385
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4108,25 +4028,25 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 0
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -4138,7 +4058,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4150,13 +4070,13 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">687
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4172,15 +4092,15 @@
 </t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1889
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -4190,7 +4110,11 @@
 </t>
         </is>
       </c>
-      <c r="Q27" s="3" t="n"/>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -4205,7 +4129,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
@@ -4251,80 +4175,85 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52940
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -4334,7 +4263,7 @@
 </t>
         </is>
       </c>
-      <c r="S28" s="8" t="inlineStr">
+      <c r="S28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">207
 </t>
@@ -4388,7 +4317,7 @@
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -4478,20 +4407,19 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6595
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
@@ -4506,9 +4434,9 @@
 </t>
         </is>
       </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -4537,46 +4465,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19524
+          <t xml:space="preserve">13348
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18168
+          <t xml:space="preserve">1098
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">474
+          <t xml:space="preserve">484
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20161
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26814
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -4594,25 +4527,23 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8365
+          <t xml:space="preserve">1854
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4200
-</t>
+          <t>434644</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -4624,7 +4555,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10820
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
@@ -4642,38 +4573,35 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>704</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18182
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9856
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3162
+          <t xml:space="preserve">31362
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">498
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4691,7 +4619,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4727,7 +4655,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -4737,10 +4665,15 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85 2
+</t>
+        </is>
+      </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -4818,8 +4751,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
-</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
@@ -4841,33 +4773,23 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
+      <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
-</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -4915,23 +4837,22 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
-</t>
+          <t>714</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -4945,17 +4866,16 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
+          <t>548</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">946
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
@@ -4969,14 +4889,13 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z32" s="3" t="n"/>
@@ -4993,21 +4912,16 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5031,13 +4945,13 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -5055,13 +4969,13 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -5073,17 +4987,16 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="R33" s="8" t="inlineStr">
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
 </t>
@@ -5113,7 +5026,7 @@
 </t>
         </is>
       </c>
-      <c r="W33" s="3" t="inlineStr">
+      <c r="W33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
@@ -5148,7 +5061,7 @@
       <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -5160,11 +5073,11 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
@@ -5214,7 +5127,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -5224,15 +5137,15 @@
 </t>
         </is>
       </c>
-      <c r="Q34" s="8" t="inlineStr">
+      <c r="Q34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">282
 </t>
         </is>
       </c>
-      <c r="R34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0216
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -5254,9 +5167,9 @@
 </t>
         </is>
       </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2846
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -5268,7 +5181,7 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -5289,7 +5202,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5307,7 +5220,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -5323,9 +5236,9 @@
 </t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5361,25 +5274,25 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="P35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="R35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1908
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -5407,7 +5320,7 @@
 </t>
         </is>
       </c>
-      <c r="W35" s="8" t="inlineStr">
+      <c r="W35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
@@ -5434,27 +5347,22 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">486
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -5472,7 +5380,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -5496,7 +5404,7 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">072
 </t>
         </is>
       </c>
@@ -5544,7 +5452,8 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
@@ -5588,13 +5497,13 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11208
+          <t xml:space="preserve">11388
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">8 82
 </t>
         </is>
       </c>
@@ -5606,62 +5515,60 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">4986
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8080
+          <t xml:space="preserve">8980
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218164
+          <t xml:space="preserve">2109
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0116
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10822
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49208
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5672,26 +5579,25 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11022
+          <t xml:space="preserve">1022
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
+          <t xml:space="preserve">2086
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>447</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
@@ -5702,7 +5608,7 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -5714,13 +5620,13 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1068
+          <t xml:space="preserve">1560
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -5776,13 +5682,13 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">951
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5792,7 +5698,7 @@
 </t>
         </is>
       </c>
-      <c r="M38" s="8" t="inlineStr">
+      <c r="M38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">165
 </t>
@@ -5830,13 +5736,12 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">387
+          <t xml:space="preserve">577
 </t>
         </is>
       </c>
@@ -5848,8 +5753,7 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
@@ -5884,126 +5788,116 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="n"/>
+      <c r="S39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="T39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">026
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="M39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="N39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8986
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">408
-</t>
-        </is>
-      </c>
-      <c r="S39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">928
-</t>
-        </is>
-      </c>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">868
-</t>
-        </is>
-      </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -6015,7 +5909,7 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -6035,13 +5929,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -6053,19 +5947,19 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -6075,15 +5969,10 @@
 </t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
+      <c r="J40" s="3" t="n"/>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
@@ -6113,19 +6002,19 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -6137,7 +6026,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">518
 </t>
         </is>
       </c>
@@ -6187,13 +6076,13 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -6211,7 +6100,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -6223,8 +6112,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>435</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -6235,7 +6123,8 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">58
+</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -6246,13 +6135,13 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -6275,16 +6164,21 @@
 </t>
         </is>
       </c>
-      <c r="S41" s="3" t="n"/>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">623
-</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1084
+          <t xml:space="preserve">625
+</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -6302,7 +6196,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -6330,12 +6224,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">304
@@ -6350,8 +6239,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -6360,19 +6248,19 @@
 </t>
         </is>
       </c>
-      <c r="H42" s="3" t="n"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">64
 </t>
         </is>
       </c>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
+      <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6393,7 +6281,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6417,8 +6305,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="S42" s="3" t="n"/>
@@ -6440,13 +6327,13 @@
 </t>
         </is>
       </c>
-      <c r="W42" s="8" t="inlineStr">
+      <c r="W42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
 </t>
         </is>
       </c>
-      <c r="X42" s="8" t="inlineStr">
+      <c r="X42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
@@ -6460,7 +6347,7 @@
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6480,21 +6367,17 @@
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n"/>
       <c r="G43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">185
@@ -6503,13 +6386,13 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6555,9 +6438,9 @@
 </t>
         </is>
       </c>
-      <c r="Q43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">094
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -6567,31 +6450,30 @@
 </t>
         </is>
       </c>
-      <c r="S43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
-</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">926
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="W43" s="8" t="inlineStr">
+          <t>264</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
 </t>
@@ -6628,14 +6510,19 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
@@ -6643,7 +6530,7 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">2170
 </t>
         </is>
       </c>
@@ -6661,29 +6548,33 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">126
 </t>
         </is>
       </c>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">164
@@ -6698,7 +6589,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -6726,22 +6617,16 @@
 </t>
         </is>
       </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
+      <c r="U44" s="3" t="n"/>
       <c r="V44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">264
 </t>
         </is>
       </c>
-      <c r="W44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>300</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
@@ -6770,40 +6655,34 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 1
-</t>
-        </is>
-      </c>
+      <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0221
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2884
+          <t xml:space="preserve">8306
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>951</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -6814,19 +6693,19 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11896
+          <t xml:space="preserve">10896
 </t>
         </is>
       </c>
@@ -6838,16 +6717,11 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11027
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179926
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="n"/>
       <c r="P45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -6856,20 +6730,17 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16620
-</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -6886,19 +6757,19 @@
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3228
+          <t xml:space="preserve">1 8
 </t>
         </is>
       </c>
@@ -6923,10 +6794,9 @@
         </is>
       </c>
       <c r="C46" s="3" t="n"/>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">719
-</t>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>619</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -6937,7 +6807,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6949,13 +6819,13 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6972,15 +6842,15 @@
 </t>
         </is>
       </c>
-      <c r="M46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">854
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -6998,7 +6868,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -7010,7 +6880,7 @@
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -7022,7 +6892,7 @@
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -7046,7 +6916,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">16 54
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_digit_manipulation.xlsx
@@ -738,112 +738,107 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">278
 </t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
 </t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">868
+</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">170
 </t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">840
 </t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">278
 </t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">205
 </t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">548
-</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
+      <c r="U4" s="3" t="n"/>
       <c r="V4" s="3" t="n"/>
       <c r="W4" s="3" t="n"/>
       <c r="X4" s="3" t="n"/>
@@ -862,7 +857,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">284
@@ -907,77 +907,82 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">836
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">548
+</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
@@ -986,7 +991,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">565
 </t>
         </is>
       </c>
@@ -1009,10 +1014,15 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -1024,7 +1034,8 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1077,7 +1088,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
@@ -1107,7 +1118,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -1119,7 +1130,7 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -1160,7 +1171,12 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">304
@@ -1173,7 +1189,12 @@
 </t>
         </is>
       </c>
-      <c r="F7" s="3" t="n"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">126
@@ -1194,7 +1215,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -1206,13 +1227,13 @@
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">074
+          <t xml:space="preserve">895
+</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -1224,7 +1245,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -1234,9 +1255,9 @@
 </t>
         </is>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">304
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">004
 </t>
         </is>
       </c>
@@ -1254,19 +1275,20 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">6564
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">258
+</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
@@ -1275,7 +1297,7 @@
 </t>
         </is>
       </c>
-      <c r="X7" s="3" t="inlineStr">
+      <c r="X7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">192
 </t>
@@ -1289,7 +1311,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -1309,31 +1331,37 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2359
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -1349,10 +1377,15 @@
 </t>
         </is>
       </c>
-      <c r="L8" s="3" t="n"/>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -1368,7 +1401,12 @@
 </t>
         </is>
       </c>
-      <c r="P8" s="3" t="n"/>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">306
@@ -1389,38 +1427,43 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">459
+          <t xml:space="preserve">426
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">420
+</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="n"/>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -1440,104 +1483,109 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1488
+</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8871
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">348
+</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">364
+</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">917
+</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">832
+</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">898
+</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4235
+</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1428
 </t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">887
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">871
-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">864
-</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">917
-</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">832
-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">098
-</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4235
-</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1928
-</t>
-        </is>
-      </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1860
+          <t xml:space="preserve">11960
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
+          <t xml:space="preserve">1826
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2631
+          <t xml:space="preserve">92551
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
@@ -1548,25 +1596,25 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">9714
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">951
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2299
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
+          <t xml:space="preserve">670
 </t>
         </is>
       </c>
@@ -1584,7 +1632,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">292
 </t>
@@ -1604,7 +1652,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -1622,13 +1670,13 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -1676,13 +1724,13 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">905
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -1712,13 +1760,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">5 9
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -1736,14 +1784,15 @@
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>35</t>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>769</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1754,18 +1803,18 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>414</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>546</t>
+          <t xml:space="preserve">154
+</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1800,7 +1849,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -1812,7 +1861,7 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -1824,21 +1873,41 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">475
-</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="n"/>
-      <c r="V11" s="3" t="n"/>
-      <c r="W11" s="3" t="n"/>
-      <c r="X11" s="3" t="n"/>
-      <c r="Y11" s="3" t="n"/>
+          <t>4254</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>1951</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">489
+</t>
+        </is>
+      </c>
       <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1853,10 +1922,15 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -1868,7 +1942,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">431
 </t>
         </is>
       </c>
@@ -1908,7 +1982,7 @@
 </t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">174
 </t>
@@ -1928,7 +2002,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1952,38 +2026,39 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="n"/>
+          <t xml:space="preserve">2571
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="W12" s="8" t="inlineStr">
+          <t>454</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">600
-</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -2003,40 +2078,40 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">60
 </t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">96
@@ -2045,7 +2120,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -2069,13 +2144,13 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2093,19 +2168,19 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">571
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -2117,7 +2192,7 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -2129,10 +2204,16 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>7640</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+          <t xml:space="preserve">600
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -2165,10 +2246,16 @@
 </t>
         </is>
       </c>
-      <c r="G14" s="3" t="n"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>478</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -2177,7 +2264,7 @@
 </t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">110
 </t>
@@ -2201,7 +2288,7 @@
 </t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">173
 </t>
@@ -2209,7 +2296,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
+          <t xml:space="preserve">7145
 </t>
         </is>
       </c>
@@ -2227,31 +2314,31 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="S14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">515
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -2269,7 +2356,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -2305,9 +2392,9 @@
 </t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">838
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -2335,10 +2422,15 @@
 </t>
         </is>
       </c>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2356,13 +2448,13 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -2392,7 +2484,7 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2404,7 +2496,7 @@
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -2416,13 +2508,13 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -2439,17 +2531,27 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10388
-</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n"/>
+          <t xml:space="preserve">1388
+</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11139
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -2461,19 +2563,18 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>30191</t>
+          <t xml:space="preserve">2882
+</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -2484,7 +2585,8 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t xml:space="preserve">920
+</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -2495,19 +2597,24 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">9094
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n"/>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182
+</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8382
+          <t xml:space="preserve">1382
 </t>
         </is>
       </c>
@@ -2525,8 +2632,7 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2662
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
@@ -2549,7 +2655,7 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>953</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -2560,7 +2666,7 @@
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -2580,7 +2686,7 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -2598,13 +2704,13 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -2633,9 +2739,9 @@
 </t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -2647,31 +2753,31 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">522
+          <t xml:space="preserve">512
 </t>
         </is>
       </c>
@@ -2689,24 +2795,25 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">155
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">604
+          <t xml:space="preserve">10685
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">810 8
 </t>
         </is>
       </c>
@@ -2723,51 +2830,56 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n"/>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>884</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>136</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>496</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2778,14 +2890,12 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">788
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
@@ -2796,14 +2906,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
-        </is>
-      </c>
-      <c r="R18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298
-</t>
+          <t>9047</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>448</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -2814,35 +2922,42 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
-</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>914</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="Y18" s="3" t="n"/>
-      <c r="Z18" s="3" t="n"/>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">007
+</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">380
+</t>
+        </is>
+      </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -2856,12 +2971,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">296
@@ -2876,7 +2986,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -2888,7 +2998,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 5
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -2906,7 +3016,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2922,21 +3032,27 @@
 </t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="n"/>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
@@ -2954,7 +3070,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
@@ -2984,13 +3100,13 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">2940
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -3007,7 +3123,12 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">106
@@ -3026,43 +3147,48 @@
 </t>
         </is>
       </c>
-      <c r="G20" s="3" t="n"/>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">874
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">008
+</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">174
 </t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -3101,13 +3227,14 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">475
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>760</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -3130,13 +3257,13 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3156,7 +3283,7 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -3192,19 +3319,18 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">008
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3216,7 +3342,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -3232,7 +3358,12 @@
 </t>
         </is>
       </c>
-      <c r="Q21" s="3" t="n"/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">200
@@ -3247,13 +3378,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2560
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
@@ -3263,7 +3394,7 @@
 </t>
         </is>
       </c>
-      <c r="W21" s="8" t="inlineStr">
+      <c r="W21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
@@ -3271,12 +3402,13 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
@@ -3299,7 +3431,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">284
@@ -3308,13 +3445,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -3350,7 +3487,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3362,7 +3499,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3386,13 +3523,13 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -3408,13 +3545,13 @@
 </t>
         </is>
       </c>
-      <c r="V22" s="8" t="inlineStr">
+      <c r="V22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
         </is>
       </c>
-      <c r="W22" s="8" t="inlineStr">
+      <c r="W22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -3422,7 +3559,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -3433,7 +3570,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">2549
 </t>
         </is>
       </c>
@@ -3450,10 +3587,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -3465,30 +3607,30 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">362
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>848</t>
+          <t xml:space="preserve">848
+</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5295
-</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">529
 </t>
         </is>
       </c>
@@ -3500,42 +3642,43 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>440</t>
+          <t xml:space="preserve">1404
+</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1039
+          <t xml:space="preserve">1034
 </t>
         </is>
       </c>
@@ -3547,41 +3690,40 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82678
-</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>976</t>
+          <t xml:space="preserve">919
+</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">11235
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">9356
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>70501</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">6528
 </t>
         </is>
       </c>
@@ -3611,9 +3753,9 @@
 </t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">375
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -3625,49 +3767,44 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">170
 </t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">054
 </t>
         </is>
       </c>
@@ -3677,9 +3814,9 @@
 </t>
         </is>
       </c>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
@@ -3697,43 +3834,43 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3750,34 +3887,34 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">19 4
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3801,35 +3938,36 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">076
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="n"/>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -3838,13 +3976,12 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="U25" s="3" t="n"/>
@@ -3856,13 +3993,26 @@
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="n"/>
-      <c r="Y25" s="3" t="n"/>
-      <c r="Z25" s="3" t="n"/>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">888
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -3876,39 +4026,34 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+      <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -3920,7 +4065,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
@@ -3942,16 +4087,21 @@
 </t>
         </is>
       </c>
-      <c r="N26" s="3" t="n"/>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -3975,18 +4125,19 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">522
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">494
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -4004,13 +4155,14 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">1128
+</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4026,27 +4178,22 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -4058,49 +4205,49 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">687
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
@@ -4112,7 +4259,8 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">214
+</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
@@ -4129,19 +4277,19 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">648
 </t>
         </is>
       </c>
@@ -4157,8 +4305,18 @@
 </t>
         </is>
       </c>
-      <c r="Y27" s="3" t="n"/>
-      <c r="Z27" s="3" t="n"/>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">640
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -4172,22 +4330,27 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -4197,9 +4360,9 @@
 </t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
@@ -4211,13 +4374,13 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4229,19 +4392,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -4271,7 +4434,7 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
@@ -4283,24 +4446,34 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="3" t="n"/>
-      <c r="Z28" s="3" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">599
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -4314,67 +4487,72 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">174
 </t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">191
@@ -4407,19 +4585,20 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t xml:space="preserve">132
+</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
@@ -4434,9 +4613,9 @@
 </t>
         </is>
       </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
+      <c r="X29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -4465,15 +4644,10 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
+      <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13348
+          <t xml:space="preserve">1332
 </t>
         </is>
       </c>
@@ -4485,60 +4659,57 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1098
+          <t xml:space="preserve">095
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">484
-</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">2800
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">914
-</t>
+          <t>94348</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>434644</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4573,35 +4744,35 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>704</t>
+          <t xml:space="preserve">108
+</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>716</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31362
+          <t xml:space="preserve">9162
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>476</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4619,7 +4790,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4643,13 +4814,13 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4665,15 +4836,10 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85 2
-</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -4685,13 +4851,13 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">2051
 </t>
         </is>
       </c>
@@ -4709,16 +4875,16 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">204
 </t>
         </is>
       </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">598
@@ -4727,7 +4893,7 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4751,12 +4917,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4776,11 +4943,15 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n"/>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">219
@@ -4795,8 +4966,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -4807,13 +4977,13 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4829,76 +4999,64 @@
 </t>
         </is>
       </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
+      <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>714</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">048
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="n"/>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="R32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">946
-</t>
-        </is>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">968
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="n"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">44 128
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="n"/>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -4915,19 +5073,19 @@
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -4951,7 +5109,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4967,15 +5125,15 @@
 </t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -4993,7 +5151,8 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">266
+</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
@@ -5004,19 +5163,19 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">560
+          <t xml:space="preserve">2560
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5026,7 +5185,7 @@
 </t>
         </is>
       </c>
-      <c r="W33" s="8" t="inlineStr">
+      <c r="W33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
@@ -5044,7 +5203,12 @@
 </t>
         </is>
       </c>
-      <c r="Z33" s="3" t="n"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -5061,112 +5225,112 @@
       <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">482
+</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">572
+</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="T34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">572
-</t>
-        </is>
-      </c>
-      <c r="U34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">246
@@ -5185,8 +5349,18 @@
 </t>
         </is>
       </c>
-      <c r="Y34" s="3" t="n"/>
-      <c r="Z34" s="3" t="n"/>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">670
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -5200,33 +5374,28 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+      <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -5254,15 +5423,15 @@
 </t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -5274,23 +5443,23 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="R35" s="8" t="inlineStr">
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
@@ -5304,7 +5473,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -5320,9 +5489,9 @@
 </t>
         </is>
       </c>
-      <c r="W35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
+      <c r="W35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0188
 </t>
         </is>
       </c>
@@ -5332,8 +5501,18 @@
 </t>
         </is>
       </c>
-      <c r="Y35" s="3" t="n"/>
-      <c r="Z35" s="3" t="n"/>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">865
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -5350,19 +5529,19 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -5398,13 +5577,13 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">072
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -5432,7 +5611,7 @@
 </t>
         </is>
       </c>
-      <c r="R36" s="3" t="inlineStr">
+      <c r="R36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">218
 </t>
@@ -5446,13 +5625,13 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -5476,7 +5655,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
@@ -5497,49 +5676,48 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11388
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 82
+          <t xml:space="preserve">88218
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4986
+          <t xml:space="preserve">456
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8980
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2109
-</t>
+          <t>409</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">1172
+</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
@@ -5550,54 +5728,53 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">1494
+</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1328
+          <t xml:space="preserve">1318
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">10822
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086
+          <t xml:space="preserve">2886
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>798</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
@@ -5608,19 +5785,19 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">9981
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1014
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1560
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -5664,7 +5841,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5682,23 +5859,18 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="M38" s="3" t="inlineStr">
+      <c r="M38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">165
 </t>
@@ -5706,7 +5878,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5736,12 +5908,13 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>885</t>
+          <t xml:space="preserve">283
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">577
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -5753,28 +5926,34 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t xml:space="preserve">220
+</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">12790 1
+</t>
+        </is>
+      </c>
+      <c r="X38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="n"/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5788,16 +5967,21 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n"/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>436</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -5808,34 +5992,28 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">80
 </t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">194
 </t>
@@ -5849,29 +6027,32 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">848
+</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="n"/>
-      <c r="S39" s="8" t="inlineStr">
+          <t>4665</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -5879,20 +6060,18 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
@@ -5909,11 +6088,15 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
-</t>
-        </is>
-      </c>
-      <c r="Z39" s="3" t="n"/>
+          <t xml:space="preserve">648
+</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -5927,94 +6110,94 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C40" s="3" t="n"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">840
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">162
 </t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="n"/>
-      <c r="K40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">080
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="N40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -6026,13 +6209,13 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
-</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">578
+</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">944
 </t>
         </is>
       </c>
@@ -6076,32 +6259,31 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -6112,7 +6294,8 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>435</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -6135,13 +6318,13 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -6151,7 +6334,12 @@
 </t>
         </is>
       </c>
-      <c r="P41" s="3" t="n"/>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">226
@@ -6160,7 +6348,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6172,19 +6360,19 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -6196,21 +6384,17 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">765
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">760
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="n"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -6225,9 +6409,9 @@
         </is>
       </c>
       <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">304
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">486
 </t>
         </is>
       </c>
@@ -6237,30 +6421,36 @@
 </t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="n"/>
+          <t xml:space="preserve">654
+</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6269,11 +6459,11 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">158
 </t>
@@ -6281,7 +6471,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -6305,10 +6495,16 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="n"/>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">520
@@ -6341,13 +6537,13 @@
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">570
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -6367,54 +6563,59 @@
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">501
+</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1744
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="F43" s="3" t="n"/>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L43" s="3" t="inlineStr">
+      <c r="L43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
         </is>
       </c>
-      <c r="M43" s="3" t="inlineStr">
+      <c r="M43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
@@ -6422,13 +6623,13 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">0250
 </t>
         </is>
       </c>
@@ -6446,13 +6647,13 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="S43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -6464,13 +6665,14 @@
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t>264</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
@@ -6487,13 +6689,13 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">570
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -6512,17 +6714,17 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
@@ -6530,33 +6732,34 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -6575,7 +6778,7 @@
 </t>
         </is>
       </c>
-      <c r="N44" s="8" t="inlineStr">
+      <c r="N44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
@@ -6583,23 +6786,23 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">1548
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="R44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">218
 </t>
@@ -6617,7 +6820,12 @@
 </t>
         </is>
       </c>
-      <c r="U44" s="3" t="n"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">264
@@ -6626,7 +6834,8 @@
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
@@ -6641,7 +6850,12 @@
 </t>
         </is>
       </c>
-      <c r="Z44" s="3" t="n"/>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -6658,54 +6872,55 @@
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11658
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1028
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8306
+          <t xml:space="preserve">1359
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">650
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>951</t>
+          <t xml:space="preserve">922
+</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">594
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10896
+          <t xml:space="preserve">1096
 </t>
         </is>
       </c>
@@ -6717,11 +6932,16 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="n"/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4990
+</t>
+        </is>
+      </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -6730,56 +6950,64 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">11911
+</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t xml:space="preserve">1152
+</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179
+          <t xml:space="preserve">5179
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1071
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">15430
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
+          <t xml:space="preserve">3929
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">644
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="n"/>
+          <t xml:space="preserve">694
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111411
+</t>
+        </is>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6796,7 +7024,8 @@
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>619</t>
+          <t xml:space="preserve">279
+</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -6807,13 +7036,13 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -6835,7 +7064,12 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72162 8
+</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">183
@@ -6848,79 +7082,84 @@
 </t>
         </is>
       </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
+      <c r="N46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">549
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="S46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">530
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">831
 </t>
         </is>
       </c>
-      <c r="P46" s="3" t="inlineStr">
+      <c r="Y46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">36
 </t>
         </is>
       </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16 54
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="n"/>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_digit_manipulation.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -738,104 +729,87 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>230</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">868
-</t>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="U4" s="3" t="n"/>
@@ -859,146 +833,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
-</t>
+          <t>548</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
-</t>
+          <t>565</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1016,146 +966,122 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>583</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1173,146 +1099,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">895
-</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">004
-</t>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>304</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="X7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>192</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>578</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1331,140 +1233,117 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2359
-</t>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>239</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
-</t>
+          <t>426</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>262</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>450</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1483,104 +1362,87 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1488
-</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8871
-</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>571</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
-</t>
+          <t>824</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
-</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>917</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
-</t>
+          <t>898</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4235
-</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11960
-</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
-</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92551
-</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1590,32 +1452,27 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9714
-</t>
+          <t>974</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">951
-</t>
+          <t>957</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1634,140 +1491,117 @@
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
-</t>
+          <t>847</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 9
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1784,10 +1618,9 @@
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>284</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1797,8 +1630,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1813,62 +1645,52 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>172</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -1883,8 +1705,7 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
@@ -1904,8 +1725,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
-</t>
+          <t>589</t>
         </is>
       </c>
       <c r="Z11" s="3" t="n"/>
@@ -1924,116 +1744,97 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">431
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2571
-</t>
+          <t>571</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
@@ -2058,8 +1859,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2078,140 +1878,117 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2230,140 +2007,117 @@
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>173</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7145
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="S14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>182</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">515
-</t>
+          <t>515</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2382,140 +2136,117 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>186</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2533,38 +2264,32 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1388
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">498
-</t>
+          <t>498</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2882
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2579,26 +2304,22 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9094
-</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -2608,26 +2329,22 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1382
-</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
-</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -2637,20 +2354,17 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2660,14 +2374,12 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>020</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2686,135 +2398,113 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>181</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">512
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10685
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810 8
-</t>
+          <t>254 1</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2832,14 +2522,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2884,8 +2572,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2900,8 +2587,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2916,8 +2602,7 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -2942,20 +2627,17 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">007
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2974,140 +2656,117 @@
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
-</t>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>296</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2940
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3125,146 +2784,122 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">874
-</t>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">475
-</t>
+          <t>475</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3283,38 +2918,32 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -3324,98 +2953,82 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3433,128 +3046,107 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>683</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
@@ -3564,14 +3156,12 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2549
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3589,38 +3179,32 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3630,62 +3214,52 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
-</t>
+          <t>529</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
-</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
-</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -3695,20 +3269,17 @@
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>915</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11235
-</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9356
-</t>
+          <t>956</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
@@ -3723,8 +3294,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6528
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3743,135 +3313,113 @@
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">054
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">841
-</t>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>281</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>117</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3889,63 +3437,53 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 4
-</t>
+          <t>19 2</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">076
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -3970,8 +3508,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -3987,8 +3524,7 @@
       <c r="U25" s="3" t="n"/>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -4003,14 +3539,12 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4029,140 +3563,117 @@
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">522
-</t>
+          <t>522</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>585</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4178,143 +3689,124 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
-</t>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>274</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4332,146 +3824,122 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">660
-</t>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>161</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">599
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4489,146 +3957,122 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>595</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>198</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4647,20 +4091,17 @@
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1332
-</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">095
-</t>
+          <t>095</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4670,8 +4111,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800
-</t>
+          <t>800</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4681,8 +4121,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -4697,14 +4136,12 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
-</t>
+          <t>834</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4714,38 +4151,32 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320
-</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
-</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2989
-</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>708</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
@@ -4755,8 +4186,7 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
@@ -4766,8 +4196,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9162
-</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4790,141 +4219,118 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2051
-</t>
+          <t>051</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>598</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4943,8 +4349,7 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4954,14 +4359,12 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -4971,39 +4374,33 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="P32" s="3" t="n"/>
@@ -5019,14 +4416,12 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>568</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
@@ -5042,14 +4437,12 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44 128
-</t>
+          <t>91 22</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -5073,140 +4466,117 @@
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="M33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>156</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2560
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">750
-</t>
+          <t>750</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5225,140 +4595,117 @@
       <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
+          <t>572</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5377,140 +4724,117 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
-</t>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>209</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>835</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="W35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0188
-</t>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>188</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5529,134 +4853,112 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="R36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>218</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="Z36" s="3" t="n"/>
@@ -5673,29 +4975,29 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88218
-</t>
+          <t>8821</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">456
-</t>
+          <t>456</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -5710,20 +5012,17 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>315</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>904</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -5738,38 +5037,32 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1318
-</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10822
-</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
-</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
-</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -5779,32 +5072,27 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1098
-</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9981
-</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1014
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5823,135 +5111,113 @@
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="M38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>165</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">861
-</t>
+          <t>861</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12790 1
-</t>
-        </is>
-      </c>
-      <c r="X38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1119
-</t>
+          <t>11 1</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5969,8 +5235,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -5980,14 +5245,12 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -6003,38 +5266,32 @@
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -6054,14 +5311,12 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
@@ -6076,20 +5331,17 @@
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="X39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>186</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">648
-</t>
+          <t>645</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
@@ -6113,134 +5365,112 @@
       <c r="C40" s="3" t="n"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
-</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">944
-</t>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>194</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="Z40" s="3" t="n"/>
@@ -6259,26 +5489,22 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">849
-</t>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -6288,110 +5514,92 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
-</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
+          <t>765</t>
         </is>
       </c>
       <c r="Z41" s="3" t="n"/>
@@ -6409,142 +5617,119 @@
         </is>
       </c>
       <c r="C42" s="3" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">486
-</t>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>286</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">940
-</t>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>140</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>158</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6563,140 +5748,117 @@
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">501
-</t>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1744
-</t>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>192</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="M43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>148</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0250
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="S43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>182</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6714,146 +5876,122 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>220</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1548
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="R44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>218</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -6869,143 +6007,124 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n"/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11658
-</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1028
-</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1359
-</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">650
-</t>
+          <t>650</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
-</t>
+          <t>613</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">594
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1096
-</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11911
-</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
-</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15430
-</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
-</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3929
-</t>
+          <t>935</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>644</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111411
-</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7024,140 +6143,117 @@
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72162 8
-</t>
+          <t>5 18</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="N46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">549
-</t>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>51 1</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="S46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>193</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
+          <t>831</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_digit_manipulation.xlsx
@@ -729,7 +729,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>563</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>390</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>310</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>186</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>081 1</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>842</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>020</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>197</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>254 1</t>
+          <t>90 21</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>162</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>001</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>282</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>136</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>220</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>956</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4260,7 +4260,7 @@
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>051</t>
+          <t>256</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
@@ -4300,12 +4300,12 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>592</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>142</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -4400,7 +4400,7 @@
       <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P32" s="3" t="n"/>
@@ -4437,12 +4437,12 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>91 22</t>
+          <t>91 191</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>262</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>198</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
@@ -4721,7 +4721,11 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
           <t>242</t>
@@ -4749,7 +4753,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -4977,7 +4981,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5052,12 +5056,12 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -5077,12 +5081,12 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>950</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -5131,7 +5135,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -5167,7 +5171,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>299</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -5202,12 +5206,12 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>11 1</t>
+          <t>011 1</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
@@ -5217,7 +5221,7 @@
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5489,7 +5493,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -5519,7 +5523,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -5574,7 +5578,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>622</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -5584,7 +5588,7 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
@@ -5599,7 +5603,7 @@
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>762</t>
         </is>
       </c>
       <c r="Z41" s="3" t="n"/>
@@ -5629,7 +5633,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -5659,7 +5663,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>174</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -5758,7 +5762,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -5813,7 +5817,7 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>304</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
@@ -5823,12 +5827,12 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>185</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>426</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
@@ -5876,12 +5880,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -5891,7 +5895,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -5901,12 +5905,12 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>152</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -5936,7 +5940,7 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -5946,7 +5950,7 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
@@ -6009,7 +6013,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6044,7 +6048,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>612</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -6064,12 +6068,12 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -6089,12 +6093,12 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
@@ -6114,7 +6118,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -6178,7 +6182,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>5 18</t>
+          <t>28 08</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6193,7 +6197,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>51 1</t>
+          <t>2011 0</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -6203,7 +6207,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>262</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -6253,7 +6257,7 @@
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/904/904_197208_SF.JPG_stage_digit_manipulation.xlsx
@@ -729,7 +729,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>583</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>318</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>081 1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>892</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>107</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>220</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>90 21</t>
+          <t>08 8</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>540</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>854</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>00</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>595</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>806</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4300,12 +4300,12 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>598</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>148</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>572</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
@@ -4400,7 +4400,7 @@
       <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>208</t>
         </is>
       </c>
       <c r="P32" s="3" t="n"/>
@@ -4437,12 +4437,12 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>91 191</t>
+          <t>00 10</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
@@ -4721,11 +4721,7 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
           <t>242</t>
@@ -4991,7 +4987,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -5061,7 +5057,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -5086,7 +5082,7 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>014</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -5171,7 +5167,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -5191,32 +5187,32 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>05 0</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
           <t>01</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t>011 1</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>111</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
@@ -5379,7 +5375,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5454,7 +5450,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
@@ -5493,7 +5489,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -5523,7 +5519,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -5578,7 +5574,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>628</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -5603,7 +5599,7 @@
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>765</t>
         </is>
       </c>
       <c r="Z41" s="3" t="n"/>
@@ -5847,7 +5843,7 @@
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>290</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -5880,7 +5876,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -5905,7 +5901,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -5940,7 +5936,7 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>840</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -5995,7 +5991,7 @@
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -6013,7 +6009,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6048,7 +6044,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>615</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -6068,7 +6064,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>105</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6113,7 +6109,7 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
@@ -6182,7 +6178,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>28 08</t>
+          <t>2 08</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6197,7 +6193,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>2011 0</t>
+          <t>200 0</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -6207,7 +6203,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
